--- a/tests/t5/oracle-columns.xlsx
+++ b/tests/t5/oracle-columns.xlsx
@@ -32,7 +32,7 @@
     <t xml:space="preserve">  Schema: USER1</t>
   </si>
   <si>
-    <t xml:space="preserve">  Exported: 2 Sep 2025 at 13:51:19 -0400</t>
+    <t xml:space="preserve">  Exported: 2 Sep 2025 at 13:56:49 -0400</t>
   </si>
   <si>
     <t xml:space="preserve">  Generated by: HotRod version 5.1.3-SNAPSHOT (build 20250902-173809)</t>
